--- a/tools/importer/reports/import-who-we-are.report.xlsx
+++ b/tools/importer/reports/import-who-we-are.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="97">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,84 @@
     <t>url</t>
   </si>
   <si>
+    <t>index.report.json</t>
+  </si>
+  <si>
+    <t>["carousel-hero","hero-marquee","columns-mosaic","carousel-article"]</t>
+  </si>
+  <si>
+    <t>index</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>homepage</t>
+  </si>
+  <si>
+    <t>2026-05-14T20:28:19.380Z</t>
+  </si>
+  <si>
+    <t>Chevron Corporation - Human Energy — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/</t>
+  </si>
+  <si>
+    <t>investors.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","carousel-article","columns-data","columns-data","cards-news","carousel-event","cards-icon","columns-stock","columns-contact","columns-contact"]</t>
+  </si>
+  <si>
+    <t>investors</t>
+  </si>
+  <si>
+    <t>2026-05-14T22:08:04.337Z</t>
+  </si>
+  <si>
+    <t>Chevron Investors: Delivering Strong Results — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/investors</t>
+  </si>
+  <si>
+    <t>sustainability.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","embed-map","cards-topic","carousel-article"]</t>
+  </si>
+  <si>
+    <t>sustainability</t>
+  </si>
+  <si>
+    <t>2026-05-14T20:00:15.122Z</t>
+  </si>
+  <si>
+    <t>Sustainability — Chevron.com — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/sustainability</t>
+  </si>
+  <si>
+    <t>what-we-do.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-mosaic","columns-mosaic","carousel-article"]</t>
+  </si>
+  <si>
+    <t>what-we-do</t>
+  </si>
+  <si>
+    <t>2026-05-14T20:00:05.630Z</t>
+  </si>
+  <si>
+    <t>What We Do — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/what-we-do</t>
+  </si>
+  <si>
     <t>who-we-are.report.json</t>
   </si>
   <si>
@@ -46,16 +124,184 @@
     <t>who-we-are</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
-    <t>2026-05-14T16:04:39.512Z</t>
+    <t>2026-05-15T20:01:30.755Z</t>
   </si>
   <si>
     <t>Who We Are — Chevron</t>
   </si>
   <si>
     <t>https://www.chevron.com/who-we-are</t>
+  </si>
+  <si>
+    <t>sustainability/climate.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","video-infographic","video-infographic","columns-strategy","cards-data","cards-data","cards-feature","quote-executive","carousel-article","columns-data"]</t>
+  </si>
+  <si>
+    <t>sustainability/climate</t>
+  </si>
+  <si>
+    <t>sustainability-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T12:47:15.848Z</t>
+  </si>
+  <si>
+    <t>Climate – Chevron.com — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/sustainability/climate</t>
+  </si>
+  <si>
+    <t>sustainability/environment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","quote-executive","carousel-article","carousel-article","carousel-article","carousel-article","cards-icon"]</t>
+  </si>
+  <si>
+    <t>sustainability/environment</t>
+  </si>
+  <si>
+    <t>2026-05-15T12:47:22.628Z</t>
+  </si>
+  <si>
+    <t>Environment | Chevron — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/sustainability/environment</t>
+  </si>
+  <si>
+    <t>sustainability/social-investment.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","cards-data","carousel-article","cards-icon","cards-icon","video-background","accordion-social","embed-video"]</t>
+  </si>
+  <si>
+    <t>sustainability/social-investment</t>
+  </si>
+  <si>
+    <t>2026-05-15T12:48:15.982Z</t>
+  </si>
+  <si>
+    <t>Social Investment | Chevron — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/sustainability/social-investment</t>
+  </si>
+  <si>
+    <t>what-we-do/energy.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-feature","columns-feature","columns-feature","columns-feature","carousel-article"]</t>
+  </si>
+  <si>
+    <t>what-we-do/energy</t>
+  </si>
+  <si>
+    <t>what-we-do-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T13:53:59.978Z</t>
+  </si>
+  <si>
+    <t>Energy Solutions — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/what-we-do/energy</t>
+  </si>
+  <si>
+    <t>what-we-do/technology-and-innovation.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","carousel-article","carousel-article","carousel-feature"]</t>
+  </si>
+  <si>
+    <t>what-we-do/technology-and-innovation</t>
+  </si>
+  <si>
+    <t>2026-05-15T13:54:13.965Z</t>
+  </si>
+  <si>
+    <t>Technology and Innovation — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/what-we-do/technology-and-innovation</t>
+  </si>
+  <si>
+    <t>who-we-are/culture.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-feature","columns-feature","columns-feature","columns-feature","carousel-article","carousel-image","carousel-feature","cards-data"]</t>
+  </si>
+  <si>
+    <t>who-we-are/culture</t>
+  </si>
+  <si>
+    <t>who-we-are-topic</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:27.138Z</t>
+  </si>
+  <si>
+    <t>Chevron Culture — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/culture</t>
+  </si>
+  <si>
+    <t>who-we-are/history.report.json</t>
+  </si>
+  <si>
+    <t>["columns-brand","columns-brand","columns-brand","columns-brand","carousel-article","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","carousel-image","tabs-timeline"]</t>
+  </si>
+  <si>
+    <t>who-we-are/history</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:35:01.308Z</t>
+  </si>
+  <si>
+    <t>Our History | Chevron — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/history</t>
+  </si>
+  <si>
+    <t>who-we-are/leadership.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","cards-data","cards-data"]</t>
+  </si>
+  <si>
+    <t>who-we-are/leadership</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:40.279Z</t>
+  </si>
+  <si>
+    <t>Chevron Leadership — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/leadership</t>
+  </si>
+  <si>
+    <t>who-we-are/our-brands.report.json</t>
+  </si>
+  <si>
+    <t>["hero-video","columns-brand","columns-brand","columns-brand","columns-brand","columns-brand","columns-mosaic"]</t>
+  </si>
+  <si>
+    <t>who-we-are/our-brands</t>
+  </si>
+  <si>
+    <t>2026-05-15T15:34:33.105Z</t>
+  </si>
+  <si>
+    <t>Our Brands — Chevron</t>
+  </si>
+  <si>
+    <t>https://www.chevron.com/who-we-are/our-brands</t>
   </si>
 </sst>
 </file>
@@ -444,16 +690,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="50" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
+    <col min="1" max="2" width="50" customWidth="1"/>
+    <col min="3" max="3" width="38" customWidth="1"/>
+    <col min="5" max="5" width="22" customWidth="1"/>
     <col min="6" max="6" width="26" customWidth="1"/>
-    <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="36" customWidth="1"/>
+    <col min="7" max="8" width="50" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -496,16 +740,354 @@
         <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>51</v>
+      </c>
+      <c r="H8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" t="s">
+        <v>56</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>62</v>
+      </c>
+      <c r="F10" t="s">
+        <v>63</v>
+      </c>
+      <c r="G10" t="s">
+        <v>64</v>
+      </c>
+      <c r="H10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" t="s">
+        <v>62</v>
+      </c>
+      <c r="F11" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>75</v>
+      </c>
+      <c r="F12" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" t="s">
+        <v>77</v>
+      </c>
+      <c r="H12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>75</v>
+      </c>
+      <c r="F13" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" t="s">
+        <v>75</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" t="s">
+        <v>92</v>
+      </c>
+      <c r="C15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D15" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
+      </c>
+      <c r="F15" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
